--- a/myapp/files/80_distances/distances_aggregate2_pValue_Risks.xlsx
+++ b/myapp/files/80_distances/distances_aggregate2_pValue_Risks.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -44,13 +44,7 @@
     <t xml:space="preserve">centertogrid</t>
   </si>
   <si>
-    <t xml:space="preserve">pooling</t>
-  </si>
-  <si>
     <t xml:space="preserve">reachedgrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted</t>
   </si>
 </sst>
 </file>
@@ -404,7 +398,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6255</v>
+        <v>417.2721</v>
       </c>
     </row>
     <row r="3">
@@ -418,7 +412,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7679</v>
+        <v>476.928</v>
       </c>
     </row>
     <row r="4">
@@ -432,7 +426,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2007</v>
+        <v>87.4432</v>
       </c>
     </row>
     <row r="5">
@@ -446,7 +440,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1495</v>
+        <v>31.5979</v>
       </c>
     </row>
     <row r="6">
@@ -460,7 +454,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6786</v>
+        <v>499.7239</v>
       </c>
     </row>
     <row r="7">
@@ -474,7 +468,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7453</v>
+        <v>260.3183</v>
       </c>
     </row>
     <row r="8">
@@ -488,7 +482,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3827</v>
+        <v>280.4038</v>
       </c>
     </row>
     <row r="9">
@@ -502,7 +496,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4449</v>
+        <v>242.4963</v>
       </c>
     </row>
     <row r="10">
@@ -516,7 +510,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4573</v>
+        <v>245.614</v>
       </c>
     </row>
     <row r="11">
@@ -530,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4222</v>
+        <v>210.8198</v>
       </c>
     </row>
     <row r="12">
@@ -544,7 +538,7 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3184</v>
+        <v>151.7323</v>
       </c>
     </row>
     <row r="13">
@@ -558,7 +552,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3801</v>
+        <v>184.6346</v>
       </c>
     </row>
     <row r="14">
@@ -572,7 +566,7 @@
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0852</v>
+        <v>405.5195</v>
       </c>
     </row>
     <row r="15">
@@ -586,7 +580,7 @@
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4115</v>
+        <v>328.3309</v>
       </c>
     </row>
     <row r="16">
@@ -600,7 +594,7 @@
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0735</v>
+        <v>453.881</v>
       </c>
     </row>
     <row r="17">
@@ -614,7 +608,7 @@
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3782</v>
+        <v>235.6121</v>
       </c>
     </row>
     <row r="18">
@@ -628,7 +622,7 @@
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0784</v>
+        <v>45.7279</v>
       </c>
     </row>
     <row r="19">
@@ -642,7 +636,7 @@
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4079</v>
+        <v>23.7311</v>
       </c>
     </row>
     <row r="20">
@@ -656,7 +650,7 @@
         <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3968</v>
+        <v>193.137</v>
       </c>
     </row>
     <row r="21">
@@ -670,315 +664,7 @@
         <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0278</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.0946</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.4051</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.0754</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.4163</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.3233</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.3915</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.4561</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.3711</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.1466</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.0965</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.3297</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.4357</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.0608</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.0171</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.1577</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.1379</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.3676</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" t="s">
-        <v>12</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.4498</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" t="s">
-        <v>12</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.6541</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" t="s">
-        <v>12</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.7729</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.3637</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.3807</v>
+        <v>194.9493</v>
       </c>
     </row>
   </sheetData>

--- a/myapp/files/80_distances/distances_aggregate2_pValue_Risks.xlsx
+++ b/myapp/files/80_distances/distances_aggregate2_pValue_Risks.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -44,7 +44,13 @@
     <t xml:space="preserve">centertogrid</t>
   </si>
   <si>
+    <t xml:space="preserve">pooling</t>
+  </si>
+  <si>
     <t xml:space="preserve">reachedgrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted</t>
   </si>
 </sst>
 </file>
@@ -398,7 +404,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>417.2721</v>
+        <v>6.7159</v>
       </c>
     </row>
     <row r="3">
@@ -412,7 +418,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>476.928</v>
+        <v>5.1484</v>
       </c>
     </row>
     <row r="4">
@@ -426,7 +432,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>87.4432</v>
+        <v>1.4509</v>
       </c>
     </row>
     <row r="5">
@@ -440,7 +446,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>31.5979</v>
+        <v>0.2874</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +460,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>499.7239</v>
+        <v>10.684</v>
       </c>
     </row>
     <row r="7">
@@ -468,7 +474,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>260.3183</v>
+        <v>3.4867</v>
       </c>
     </row>
     <row r="8">
@@ -482,7 +488,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>280.4038</v>
+        <v>5.5095</v>
       </c>
     </row>
     <row r="9">
@@ -496,7 +502,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>242.4963</v>
+        <v>2.8706</v>
       </c>
     </row>
     <row r="10">
@@ -510,7 +516,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>245.614</v>
+        <v>3.9792</v>
       </c>
     </row>
     <row r="11">
@@ -524,7 +530,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>210.8198</v>
+        <v>2.8681</v>
       </c>
     </row>
     <row r="12">
@@ -538,7 +544,7 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>151.7323</v>
+        <v>5.1324</v>
       </c>
     </row>
     <row r="13">
@@ -552,7 +558,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>184.6346</v>
+        <v>1.6578</v>
       </c>
     </row>
     <row r="14">
@@ -565,8 +571,8 @@
       <c r="C14" t="s">
         <v>10</v>
       </c>
-      <c r="D14" t="n">
-        <v>405.5195</v>
+      <c r="D14" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="15">
@@ -579,8 +585,8 @@
       <c r="C15" t="s">
         <v>10</v>
       </c>
-      <c r="D15" t="n">
-        <v>328.3309</v>
+      <c r="D15" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="16">
@@ -593,8 +599,8 @@
       <c r="C16" t="s">
         <v>10</v>
       </c>
-      <c r="D16" t="n">
-        <v>453.881</v>
+      <c r="D16" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="17">
@@ -607,8 +613,8 @@
       <c r="C17" t="s">
         <v>10</v>
       </c>
-      <c r="D17" t="n">
-        <v>235.6121</v>
+      <c r="D17" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="18">
@@ -621,8 +627,8 @@
       <c r="C18" t="s">
         <v>10</v>
       </c>
-      <c r="D18" t="n">
-        <v>45.7279</v>
+      <c r="D18" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="19">
@@ -635,8 +641,8 @@
       <c r="C19" t="s">
         <v>10</v>
       </c>
-      <c r="D19" t="n">
-        <v>23.7311</v>
+      <c r="D19" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="20">
@@ -649,8 +655,8 @@
       <c r="C20" t="s">
         <v>10</v>
       </c>
-      <c r="D20" t="n">
-        <v>193.137</v>
+      <c r="D20" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="21">
@@ -663,8 +669,316 @@
       <c r="C21" t="s">
         <v>10</v>
       </c>
-      <c r="D21" t="n">
-        <v>194.9493</v>
+      <c r="D21" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7.2684</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4.162</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7.1049</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.607</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.6784</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.2183</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4.0583</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.5668</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="n">
+        <v>17.309</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.5323</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.7959</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.2647</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4.8574</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.8787</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7.6349</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4.9671</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8.0527</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4.2524</v>
       </c>
     </row>
   </sheetData>

--- a/myapp/files/80_distances/distances_aggregate2_pValue_Risks.xlsx
+++ b/myapp/files/80_distances/distances_aggregate2_pValue_Risks.xlsx
@@ -404,7 +404,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7159</v>
+        <v>0.3368</v>
       </c>
     </row>
     <row r="3">
@@ -418,7 +418,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1484</v>
+        <v>0.2867</v>
       </c>
     </row>
     <row r="4">
@@ -432,7 +432,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4509</v>
+        <v>0.1094</v>
       </c>
     </row>
     <row r="5">
@@ -446,7 +446,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2874</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="6">
@@ -460,7 +460,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>10.684</v>
+        <v>0.3867</v>
       </c>
     </row>
     <row r="7">
@@ -474,7 +474,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4867</v>
+        <v>0.3067</v>
       </c>
     </row>
     <row r="8">
@@ -488,7 +488,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>5.5095</v>
+        <v>0.2489</v>
       </c>
     </row>
     <row r="9">
@@ -502,7 +502,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8706</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="10">
@@ -516,7 +516,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>3.9792</v>
+        <v>0.3067</v>
       </c>
     </row>
     <row r="11">
@@ -530,7 +530,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>2.8681</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -544,7 +544,7 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>5.1324</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="13">
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6578</v>
+        <v>0.1067</v>
       </c>
     </row>
     <row r="14">
@@ -571,8 +571,8 @@
       <c r="C14" t="s">
         <v>10</v>
       </c>
-      <c r="D14" t="e">
-        <v>#NUM!</v>
+      <c r="D14" t="n">
+        <v>0.5559</v>
       </c>
     </row>
     <row r="15">
@@ -585,8 +585,8 @@
       <c r="C15" t="s">
         <v>10</v>
       </c>
-      <c r="D15" t="e">
-        <v>#NUM!</v>
+      <c r="D15" t="n">
+        <v>0.7321</v>
       </c>
     </row>
     <row r="16">
@@ -599,8 +599,8 @@
       <c r="C16" t="s">
         <v>10</v>
       </c>
-      <c r="D16" t="e">
-        <v>#NUM!</v>
+      <c r="D16" t="n">
+        <v>0.5183</v>
       </c>
     </row>
     <row r="17">
@@ -613,8 +613,8 @@
       <c r="C17" t="s">
         <v>10</v>
       </c>
-      <c r="D17" t="e">
-        <v>#NUM!</v>
+      <c r="D17" t="n">
+        <v>0.7467</v>
       </c>
     </row>
     <row r="18">
@@ -627,8 +627,8 @@
       <c r="C18" t="s">
         <v>10</v>
       </c>
-      <c r="D18" t="e">
-        <v>#NUM!</v>
+      <c r="D18" t="n">
+        <v>0.6527</v>
       </c>
     </row>
     <row r="19">
@@ -641,8 +641,8 @@
       <c r="C19" t="s">
         <v>10</v>
       </c>
-      <c r="D19" t="e">
-        <v>#NUM!</v>
+      <c r="D19" t="n">
+        <v>0.8394</v>
       </c>
     </row>
     <row r="20">
@@ -655,8 +655,8 @@
       <c r="C20" t="s">
         <v>10</v>
       </c>
-      <c r="D20" t="e">
-        <v>#NUM!</v>
+      <c r="D20" t="n">
+        <v>0.8927</v>
       </c>
     </row>
     <row r="21">
@@ -669,8 +669,8 @@
       <c r="C21" t="s">
         <v>10</v>
       </c>
-      <c r="D21" t="e">
-        <v>#NUM!</v>
+      <c r="D21" t="n">
+        <v>0.9194</v>
       </c>
     </row>
     <row r="22">
@@ -683,8 +683,8 @@
       <c r="C22" t="s">
         <v>10</v>
       </c>
-      <c r="D22" t="e">
-        <v>#NUM!</v>
+      <c r="D22" t="n">
+        <v>0.7136</v>
       </c>
     </row>
     <row r="23">
@@ -697,8 +697,8 @@
       <c r="C23" t="s">
         <v>10</v>
       </c>
-      <c r="D23" t="e">
-        <v>#NUM!</v>
+      <c r="D23" t="n">
+        <v>0.8509</v>
       </c>
     </row>
     <row r="24">
@@ -711,8 +711,8 @@
       <c r="C24" t="s">
         <v>10</v>
       </c>
-      <c r="D24" t="e">
-        <v>#NUM!</v>
+      <c r="D24" t="n">
+        <v>0.5094</v>
       </c>
     </row>
     <row r="25">
@@ -725,8 +725,8 @@
       <c r="C25" t="s">
         <v>10</v>
       </c>
-      <c r="D25" t="e">
-        <v>#NUM!</v>
+      <c r="D25" t="n">
+        <v>0.7454</v>
       </c>
     </row>
     <row r="26">
@@ -740,7 +740,7 @@
         <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>7.2684</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="27">
@@ -754,7 +754,7 @@
         <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>4.162</v>
+        <v>0.1709</v>
       </c>
     </row>
     <row r="28">
@@ -768,7 +768,7 @@
         <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>7.1049</v>
+        <v>0.2457</v>
       </c>
     </row>
     <row r="29">
@@ -782,7 +782,7 @@
         <v>11</v>
       </c>
       <c r="D29" t="n">
-        <v>3.607</v>
+        <v>0.1909</v>
       </c>
     </row>
     <row r="30">
@@ -796,7 +796,7 @@
         <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6784</v>
+        <v>0.0886</v>
       </c>
     </row>
     <row r="31">
@@ -810,7 +810,7 @@
         <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2183</v>
+        <v>0.0463</v>
       </c>
     </row>
     <row r="32">
@@ -824,7 +824,7 @@
         <v>11</v>
       </c>
       <c r="D32" t="n">
-        <v>4.0583</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="33">
@@ -838,7 +838,7 @@
         <v>11</v>
       </c>
       <c r="D33" t="n">
-        <v>1.5668</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="34">
@@ -852,7 +852,7 @@
         <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>17.309</v>
+        <v>0.0588</v>
       </c>
     </row>
     <row r="35">
@@ -866,7 +866,7 @@
         <v>12</v>
       </c>
       <c r="D35" t="n">
-        <v>1.5323</v>
+        <v>0.0239</v>
       </c>
     </row>
     <row r="36">
@@ -880,7 +880,7 @@
         <v>12</v>
       </c>
       <c r="D36" t="n">
-        <v>0.7959</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="37">
@@ -894,7 +894,7 @@
         <v>12</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2647</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="38">
@@ -908,7 +908,7 @@
         <v>12</v>
       </c>
       <c r="D38" t="n">
-        <v>4.8574</v>
+        <v>0.2387</v>
       </c>
     </row>
     <row r="39">
@@ -922,7 +922,7 @@
         <v>12</v>
       </c>
       <c r="D39" t="n">
-        <v>2.8787</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="40">
@@ -936,7 +936,7 @@
         <v>12</v>
       </c>
       <c r="D40" t="n">
-        <v>7.6349</v>
+        <v>0.3833</v>
       </c>
     </row>
     <row r="41">
@@ -950,7 +950,7 @@
         <v>12</v>
       </c>
       <c r="D41" t="n">
-        <v>4.9671</v>
+        <v>0.2707</v>
       </c>
     </row>
     <row r="42">
@@ -964,7 +964,7 @@
         <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>8.0527</v>
+        <v>0.2043</v>
       </c>
     </row>
     <row r="43">
@@ -978,7 +978,7 @@
         <v>12</v>
       </c>
       <c r="D43" t="n">
-        <v>4.2524</v>
+        <v>0.1581</v>
       </c>
     </row>
   </sheetData>
